--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649800</v>
+        <v>123649769</v>
       </c>
       <c r="B4" t="n">
-        <v>105485</v>
+        <v>98396</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R4" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123649769</v>
+        <v>123649809</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>97354</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,57 +1035,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>224364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R5" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1147,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649809</v>
+        <v>123649800</v>
       </c>
       <c r="B6" t="n">
-        <v>97337</v>
+        <v>105502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,22 +1147,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224364</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649769</v>
+        <v>123649800</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R4" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>123649809</v>
       </c>
       <c r="B5" t="n">
-        <v>97354</v>
+        <v>97371</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649800</v>
+        <v>123649769</v>
       </c>
       <c r="B6" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1183,17 +1183,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R6" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>123649800</v>
       </c>
       <c r="B4" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>123649809</v>
       </c>
       <c r="B5" t="n">
-        <v>97371</v>
+        <v>97373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>123649769</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649800</v>
+        <v>123649769</v>
       </c>
       <c r="B4" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R4" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>123649809</v>
       </c>
       <c r="B5" t="n">
-        <v>97373</v>
+        <v>96961</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649769</v>
+        <v>123649800</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1183,17 +1183,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R6" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649769</v>
+        <v>123649800</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R4" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649800</v>
+        <v>123649769</v>
       </c>
       <c r="B6" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,35 +1143,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1183,17 +1183,17 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R6" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649800</v>
+        <v>123649769</v>
       </c>
       <c r="B4" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,35 +911,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -951,17 +951,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R4" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123649809</v>
+        <v>123649800</v>
       </c>
       <c r="B5" t="n">
-        <v>96961</v>
+        <v>105095</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,22 +1039,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224364</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1131,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649769</v>
+        <v>123649809</v>
       </c>
       <c r="B6" t="n">
-        <v>98079</v>
+        <v>96961</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,57 +1159,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>224364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R6" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649769</v>
+        <v>123649809</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>96961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,57 +911,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>224364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566267</v>
+        <v>566312</v>
       </c>
       <c r="R4" t="n">
-        <v>6512752</v>
+        <v>6512699</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1147,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649809</v>
+        <v>123649769</v>
       </c>
       <c r="B6" t="n">
-        <v>96961</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,41 +1143,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R6" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>97570875</v>
       </c>
       <c r="B2" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566172.4450310247</v>
+        <v>566172</v>
       </c>
       <c r="R2" t="n">
-        <v>6513255.71231507</v>
+        <v>6513255</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-04-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97571001</v>
+        <v>97571124</v>
       </c>
       <c r="B3" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2818</v>
+        <v>1590</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566177.1757091365</v>
+        <v>566172</v>
       </c>
       <c r="R3" t="n">
-        <v>6513252.679432387</v>
+        <v>6513256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-04-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-04-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123649800</v>
+        <v>97571001</v>
       </c>
       <c r="B4" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,53 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566312</v>
+        <v>566177</v>
       </c>
       <c r="R4" t="n">
-        <v>6512699</v>
+        <v>6513252</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-04-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,93 +948,78 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123649769</v>
+        <v>106457693</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1380 m, Ög</t>
+          <t>Ålgöl, Trehörningen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566267</v>
+        <v>566237</v>
       </c>
       <c r="R5" t="n">
-        <v>6512752</v>
+        <v>6513036</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1109,12 +1043,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-04-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>RVNO inv</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,77 +1062,82 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Håkan Svensson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mirjam Ideström</t>
+          <t>Håkan Svensson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123649809</v>
+        <v>123649769</v>
       </c>
       <c r="B6" t="n">
-        <v>96983</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stärkerstorp NV 1320 m, Ög</t>
+          <t>Stärkerstorp NV 1380 m, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>566312</v>
+        <v>566267</v>
       </c>
       <c r="R6" t="n">
-        <v>6512699</v>
+        <v>6512752</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,6 +1196,228 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123649800</v>
+      </c>
+      <c r="B7" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566312</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6512699</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123649809</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Stärkerstorp NV 1320 m, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566312</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6512699</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mirjam Ideström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14619-2025 artfynd.xlsx
+++ b/artfynd/A 14619-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97570875</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571124</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571001</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106457693</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1196,6 +1221,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123649769</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123649800</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1418,8 +1453,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123649809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>